--- a/EFI.xlsx
+++ b/EFI.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/459ad6f1699fcb6e/Documents/My Data Sources/"/>
     </mc:Choice>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="215">
   <si>
     <t>How do I reactivate Duo on a new mobile phone?</t>
   </si>
@@ -564,12 +564,283 @@
   </si>
   <si>
     <t>Summary counts. To Do 3, In Progress 2, Done 1 among EFI-3 to EFI-8</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@3dffc764 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@63cf9de0 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@1e01b133 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@4b7ed03e (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@3babcaed (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@370225c7 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@1cb849b2 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@14d18029 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@727f36dd (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@4ef28dc4 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@4e4c05a0 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@1ec09a68 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@528ef230 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@6d3a56ea (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@4cb45048 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@17c7cc93 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@54d8236c (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@81a193b (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@644e9953 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@5b9815b6 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@327fa027 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@3a4e3343 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@79200f8 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@30075210 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@38c408c7 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@54eaf69d (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@41991619 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@509b760e (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@3a103112 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@7500a106 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:46285}, goog:processID: 2747, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:46285/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2e6bd9dab29d5dac256ef45bb8b9d697</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@ab3cd69 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:38607}, goog:processID: 3490, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:38607/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: aad6d88e02818b07056835a3a79e8493</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Chatbot input was not found after timeout.</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@69b1e76b (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:36949}, goog:processID: 4023, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:36949/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 2aef80b78f305cd54f37f8f5ae21cf26</t>
+  </si>
+  <si>
+    <t>EXCEPTION: Expected condition failed: waiting for com.chatbot.tests.EFI$$Lambda/0x00007f162038ab90@55bd7391 (tried for 45 second(s) with 500 milliseconds interval)
+Build info: version: '4.29.0', revision: '5fc1ec94cb'
+System info: os.name: 'Linux', os.arch: 'amd64', os.version: '6.17.0-1022-azure', java.version: '21.0.12.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 152.0.7977.82, chrome: {chromedriverVersion: 152.0.7977.82 (d04cdb24d67b..., userDataDir: /tmp/org.chromium.Chromium....}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:42655}, goog:processID: 4632, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: linux, proxy: Proxy(), se:cdp: ws://localhost:42655/devtoo..., se:cdpVersion: 152.0.7977.82, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 255f3d9112453b7be4e9c173c8a1184d</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1691,8 +1962,12 @@
       <c r="I2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+      <c r="J2" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -1722,8 +1997,12 @@
       <c r="I3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="J3" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
@@ -1753,8 +2032,12 @@
       <c r="I4" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
+      <c r="J4" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
@@ -1784,8 +2067,12 @@
       <c r="I5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="J5" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
@@ -1815,8 +2102,12 @@
       <c r="I6" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
@@ -1846,8 +2137,12 @@
       <c r="I7" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="J7" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
@@ -1877,8 +2172,12 @@
       <c r="I8" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
+      <c r="J8" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
@@ -1908,8 +2207,12 @@
       <c r="I9" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
+      <c r="J9" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
@@ -1939,8 +2242,12 @@
       <c r="I10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
+      <c r="J10" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
@@ -1970,8 +2277,12 @@
       <c r="I11" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
+      <c r="J11" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
@@ -2001,8 +2312,12 @@
       <c r="I12" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
+      <c r="J12" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
@@ -2032,8 +2347,12 @@
       <c r="I13" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
+      <c r="J13" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
@@ -2063,8 +2382,12 @@
       <c r="I14" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
+      <c r="J14" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
@@ -2078,8 +2401,12 @@
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
+      <c r="J15" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="27"/>
@@ -2093,8 +2420,12 @@
       <c r="G16" s="27"/>
       <c r="H16" s="27"/>
       <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
+      <c r="J16" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
@@ -2124,8 +2455,12 @@
       <c r="I17" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
+      <c r="J17" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A18" s="26"/>
@@ -2139,8 +2474,12 @@
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
+      <c r="J18" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="27"/>
@@ -2154,8 +2493,12 @@
       <c r="G19" s="27"/>
       <c r="H19" s="27"/>
       <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
+      <c r="J19" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="K19" s="27" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="20" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
@@ -2185,8 +2528,12 @@
       <c r="I20" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
+      <c r="J20" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A21" s="26"/>
@@ -2200,8 +2547,12 @@
       <c r="G21" s="26"/>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
+      <c r="J21" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="27"/>
@@ -2215,8 +2566,12 @@
       <c r="G22" s="27"/>
       <c r="H22" s="27"/>
       <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
+      <c r="J22" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="K22" s="27" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="23" spans="1:11" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
@@ -2246,8 +2601,12 @@
       <c r="I23" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
+      <c r="J23" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="24" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A24" s="23"/>
@@ -2261,8 +2620,12 @@
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
+      <c r="J24" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="25" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="24"/>
@@ -2276,8 +2639,12 @@
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
+      <c r="J25" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="K25" s="24" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="26" spans="1:11" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
@@ -2307,8 +2674,12 @@
       <c r="I26" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
+      <c r="J26" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="27" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="23"/>
@@ -2322,8 +2693,12 @@
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
+      <c r="J27" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="28" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="24"/>
@@ -2337,8 +2712,12 @@
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
+      <c r="J28" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="K28" s="24" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="29" spans="1:11" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
@@ -2368,8 +2747,12 @@
       <c r="I29" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
+      <c r="J29" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A30" s="23"/>
@@ -2383,8 +2766,12 @@
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
+      <c r="J30" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="K30" s="23" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="31" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="24"/>
@@ -2398,8 +2785,12 @@
       <c r="G31" s="24"/>
       <c r="H31" s="24"/>
       <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
+      <c r="J31" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="K31" s="24" t="s">
+        <v>181</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="60">
@@ -2536,8 +2927,12 @@
       <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2567,8 +2962,12 @@
       <c r="I3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2598,8 +2997,12 @@
       <c r="I4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -2629,8 +3032,12 @@
       <c r="I5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -2660,8 +3067,12 @@
       <c r="I6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -2691,8 +3102,12 @@
       <c r="I7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -2722,8 +3137,12 @@
       <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -2753,8 +3172,12 @@
       <c r="I9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -2784,8 +3207,12 @@
       <c r="I10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
@@ -2815,8 +3242,12 @@
       <c r="I11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="J11" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -2846,8 +3277,12 @@
       <c r="I12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="J12" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
@@ -2877,8 +3312,12 @@
       <c r="I13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="29" t="s">
@@ -2908,8 +3347,12 @@
       <c r="I14" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
+      <c r="J14" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A15" s="30"/>
@@ -2923,8 +3366,12 @@
       <c r="G15" s="30"/>
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
+      <c r="J15" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K15" s="30" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="31"/>
@@ -2938,8 +3385,12 @@
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
       <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
+      <c r="J16" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="29" t="s">
@@ -2969,8 +3420,12 @@
       <c r="I17" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
+      <c r="J17" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A18" s="30"/>
@@ -2984,8 +3439,12 @@
       <c r="G18" s="30"/>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
+      <c r="J18" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="31"/>
@@ -2999,8 +3458,12 @@
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
       <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
+      <c r="J19" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="20" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="29" t="s">
@@ -3030,8 +3493,12 @@
       <c r="I20" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
+      <c r="J20" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K20" s="29" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="30"/>
@@ -3045,8 +3512,12 @@
       <c r="G21" s="30"/>
       <c r="H21" s="30"/>
       <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
+      <c r="J21" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="31"/>
@@ -3060,8 +3531,12 @@
       <c r="G22" s="31"/>
       <c r="H22" s="31"/>
       <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
+      <c r="J22" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="K22" s="31" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="23" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
@@ -3091,8 +3566,12 @@
       <c r="I23" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="J23" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="24" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="33"/>
@@ -3106,8 +3585,12 @@
       <c r="G24" s="33"/>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
+      <c r="J24" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K24" s="33" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="25" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34"/>
@@ -3121,8 +3604,12 @@
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
+      <c r="J25" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="K25" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="26" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
@@ -3152,8 +3639,12 @@
       <c r="I26" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
+      <c r="J26" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="27" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="33"/>
@@ -3167,8 +3658,12 @@
       <c r="G27" s="33"/>
       <c r="H27" s="33"/>
       <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
+      <c r="J27" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K27" s="33" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="28" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="34"/>
@@ -3182,8 +3677,12 @@
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
+      <c r="J28" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="29" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
@@ -3213,8 +3712,12 @@
       <c r="I29" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
+      <c r="J29" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="K29" s="32" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A30" s="33"/>
@@ -3228,8 +3731,12 @@
       <c r="G30" s="33"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
+      <c r="J30" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K30" s="33" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="31" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34"/>
@@ -3243,8 +3750,12 @@
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
       <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
+      <c r="J31" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="K31" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="60">
@@ -3381,8 +3892,12 @@
       <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -3412,8 +3927,12 @@
       <c r="I3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3443,8 +3962,12 @@
       <c r="I4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -3474,8 +3997,12 @@
       <c r="I5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -3505,8 +4032,12 @@
       <c r="I6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -3536,8 +4067,12 @@
       <c r="I7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -3567,8 +4102,12 @@
       <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -3598,8 +4137,12 @@
       <c r="I9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -3629,8 +4172,12 @@
       <c r="I10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
@@ -3660,8 +4207,12 @@
       <c r="I11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="J11" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -3691,8 +4242,12 @@
       <c r="I12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="J12" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
@@ -3722,8 +4277,12 @@
       <c r="I13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="29" t="s">
@@ -3753,8 +4312,12 @@
       <c r="I14" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
+      <c r="J14" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="144" x14ac:dyDescent="0.3">
       <c r="A15" s="30"/>
@@ -3768,8 +4331,12 @@
       <c r="G15" s="30"/>
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
+      <c r="J15" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K15" s="30" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="31"/>
@@ -3783,8 +4350,12 @@
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
       <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
+      <c r="J16" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="29" t="s">
@@ -3814,8 +4385,12 @@
       <c r="I17" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
+      <c r="J17" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A18" s="30"/>
@@ -3829,8 +4404,12 @@
       <c r="G18" s="30"/>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
+      <c r="J18" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="31"/>
@@ -3844,8 +4423,12 @@
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
       <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
+      <c r="J19" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="20" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="29" t="s">
@@ -3875,8 +4458,12 @@
       <c r="I20" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
+      <c r="J20" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K20" s="29" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A21" s="30"/>
@@ -3890,8 +4477,12 @@
       <c r="G21" s="30"/>
       <c r="H21" s="30"/>
       <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
+      <c r="J21" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="31"/>
@@ -3905,8 +4496,12 @@
       <c r="G22" s="31"/>
       <c r="H22" s="31"/>
       <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
+      <c r="J22" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="K22" s="31" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="23" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
@@ -3936,8 +4531,12 @@
       <c r="I23" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="J23" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="24" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A24" s="33"/>
@@ -3951,8 +4550,12 @@
       <c r="G24" s="33"/>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
+      <c r="J24" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K24" s="33" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="25" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="34"/>
@@ -3966,8 +4569,12 @@
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
+      <c r="J25" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="K25" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="26" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
@@ -3997,8 +4604,12 @@
       <c r="I26" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
+      <c r="J26" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="27" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="33"/>
@@ -4012,8 +4623,12 @@
       <c r="G27" s="33"/>
       <c r="H27" s="33"/>
       <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
+      <c r="J27" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K27" s="33" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="28" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="34"/>
@@ -4027,8 +4642,12 @@
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
+      <c r="J28" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="29" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
@@ -4058,8 +4677,12 @@
       <c r="I29" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
+      <c r="J29" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="K29" s="32" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A30" s="33"/>
@@ -4073,8 +4696,12 @@
       <c r="G30" s="33"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
+      <c r="J30" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K30" s="33" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="31" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34"/>
@@ -4088,8 +4715,12 @@
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
       <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
+      <c r="J31" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="K31" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="60">
@@ -4226,8 +4857,12 @@
       <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -4257,8 +4892,12 @@
       <c r="I3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4288,8 +4927,12 @@
       <c r="I4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -4319,8 +4962,12 @@
       <c r="I5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -4350,8 +4997,12 @@
       <c r="I6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -4381,8 +5032,12 @@
       <c r="I7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -4412,8 +5067,12 @@
       <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -4443,8 +5102,12 @@
       <c r="I9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -4474,8 +5137,12 @@
       <c r="I10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
@@ -4505,8 +5172,12 @@
       <c r="I11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="J11" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -4536,8 +5207,12 @@
       <c r="I12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="J12" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
@@ -4567,8 +5242,12 @@
       <c r="I13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="29" t="s">
@@ -4598,8 +5277,12 @@
       <c r="I14" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
+      <c r="J14" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" s="30"/>
@@ -4613,8 +5296,12 @@
       <c r="G15" s="30"/>
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
+      <c r="J15" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K15" s="30" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="31"/>
@@ -4628,8 +5315,12 @@
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
       <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
+      <c r="J16" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="29" t="s">
@@ -4659,8 +5350,12 @@
       <c r="I17" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
+      <c r="J17" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A18" s="30"/>
@@ -4674,8 +5369,12 @@
       <c r="G18" s="30"/>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
+      <c r="J18" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="31"/>
@@ -4689,8 +5388,12 @@
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
       <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
+      <c r="J19" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="20" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="29" t="s">
@@ -4720,8 +5423,12 @@
       <c r="I20" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
+      <c r="J20" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K20" s="29" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A21" s="30"/>
@@ -4735,8 +5442,12 @@
       <c r="G21" s="30"/>
       <c r="H21" s="30"/>
       <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
+      <c r="J21" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="31"/>
@@ -4750,8 +5461,12 @@
       <c r="G22" s="31"/>
       <c r="H22" s="31"/>
       <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
+      <c r="J22" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="K22" s="31" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="23" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
@@ -4781,8 +5496,12 @@
       <c r="I23" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="J23" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="24" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A24" s="33"/>
@@ -4796,8 +5515,12 @@
       <c r="G24" s="33"/>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
+      <c r="J24" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K24" s="33" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="25" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34"/>
@@ -4811,8 +5534,12 @@
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
+      <c r="J25" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="K25" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="26" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
@@ -4842,8 +5569,12 @@
       <c r="I26" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
+      <c r="J26" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="27" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="33"/>
@@ -4857,8 +5588,12 @@
       <c r="G27" s="33"/>
       <c r="H27" s="33"/>
       <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
+      <c r="J27" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K27" s="33" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="28" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="34"/>
@@ -4872,8 +5607,12 @@
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
+      <c r="J28" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="29" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
@@ -4903,8 +5642,12 @@
       <c r="I29" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
+      <c r="J29" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="K29" s="32" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A30" s="33"/>
@@ -4918,8 +5661,12 @@
       <c r="G30" s="33"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
+      <c r="J30" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K30" s="33" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="31" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="34"/>
@@ -4933,8 +5680,12 @@
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
       <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
+      <c r="J31" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="K31" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="60">
@@ -5005,7 +5756,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530F565F-DADC-4C72-BAFF-5005D37689B1}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -5029,6 +5780,12 @@
       <c r="C2" s="28" t="s">
         <v>161</v>
       </c>
+      <c r="D2" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>181</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="28">
@@ -5040,6 +5797,12 @@
       <c r="C3" s="28" t="s">
         <v>163</v>
       </c>
+      <c r="D3" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>181</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="28">
@@ -5051,6 +5814,12 @@
       <c r="C4" s="28" t="s">
         <v>165</v>
       </c>
+      <c r="D4" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>181</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="28">
@@ -5062,6 +5831,12 @@
       <c r="C5" s="28" t="s">
         <v>167</v>
       </c>
+      <c r="D5" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>181</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="28">
@@ -5073,6 +5848,12 @@
       <c r="C6" s="28" t="s">
         <v>169</v>
       </c>
+      <c r="D6" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>181</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="28">
@@ -5084,6 +5865,12 @@
       <c r="C7" s="28" t="s">
         <v>171</v>
       </c>
+      <c r="D7" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>181</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="28">
@@ -5095,6 +5882,12 @@
       <c r="C8" s="28" t="s">
         <v>173</v>
       </c>
+      <c r="D8" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>181</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="28">
@@ -5106,6 +5899,12 @@
       <c r="C9" s="28" t="s">
         <v>175</v>
       </c>
+      <c r="D9" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>181</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="28">
@@ -5117,6 +5916,12 @@
       <c r="C10" s="28" t="s">
         <v>177</v>
       </c>
+      <c r="D10" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>181</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="28">
@@ -5127,6 +5932,12 @@
       </c>
       <c r="C11" s="28" t="s">
         <v>179</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
